--- a/Deliverability_Reachability_Calculator01.xlsx
+++ b/Deliverability_Reachability_Calculator01.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dan\Documents\Fent isofl\Neuroprotection\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Evan Doubovikov\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:20001_{CE9C975C-1F24-4863-B8EC-234E34156120}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D81550A-55DE-4CF2-BD54-FCF63A3A4EFF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6750" yWindow="1965" windowWidth="32580" windowHeight="17595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" r:id="rId1"/>
@@ -20,20 +20,11 @@
     <sheet name="Notes" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="425" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="426" uniqueCount="163">
   <si>
     <t>Stroke Neuroprotection Deliverability (Reachability) Calculator</t>
   </si>
@@ -519,6 +510,9 @@
   </si>
   <si>
     <t>7) This workbook is an optimistic upper-bound steady-state screen. Finite or declining systemic exposure will generally reduce centre delivery further.</t>
+  </si>
+  <si>
+    <t>Authors: Daniil P. Aksenov, Zhiyuan Yu, Evan D. Doubovikov, Shakeel Chowdhry, Steven Greenberg, Julian E. Bailes</t>
   </si>
 </sst>
 </file>
@@ -653,7 +647,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -681,31 +675,18 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4CCCC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="4">
     <dxf>
       <fill>
         <patternFill>
@@ -1356,7 +1337,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:G38"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1366,353 +1347,329 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="25" t="s">
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+    </row>
+    <row r="2" spans="1:7" ht="19.5" x14ac:dyDescent="0.3">
+      <c r="A2" s="22" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" s="27" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="23"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="24" t="s">
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="23"/>
-      <c r="C4" s="23"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="36.75" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="7" spans="1:7" ht="36.75" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B7" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B9" s="4">
         <v>65</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C9" s="3" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B10" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C10" s="3" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+    <row r="11" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="B10" s="6">
-        <f>IF(B9&lt;&gt;"",B9,IF(B8&lt;&gt;"",(3*B8*1000/(4*PI()))^(1/3),""))</f>
+      <c r="B11" s="6">
+        <f>IF(B10&lt;&gt;"",B10,IF(B9&lt;&gt;"",(3*B9*1000/(4*PI()))^(1/3),""))</f>
         <v>24.942591981125844</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C11" s="3" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="7">
+      <c r="B12" s="7">
         <v>0.01</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C12" s="3" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="B12" s="8" t="str">
-        <f>B5&amp;" | "&amp;B6</f>
-        <v>MgSO4 | Mid-case</v>
-      </c>
-      <c r="C12" s="9"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="10">
-        <f>VLOOKUP(B12,DrugParams!$A$2:$F$19,4,FALSE)</f>
-        <v>387.28</v>
+        <v>21</v>
+      </c>
+      <c r="B13" s="8" t="str">
+        <f>B6&amp;" | "&amp;B7</f>
+        <v>MgSO4 | Mid-case</v>
       </c>
       <c r="C13" s="9"/>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="B14" s="10">
+        <f>VLOOKUP(B13,DrugParams!$A$2:$F$19,4,FALSE)</f>
+        <v>387.28</v>
+      </c>
+      <c r="C14" s="9"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="11">
-        <f>VLOOKUP(B12,DrugParams!$A$2:$F$19,5,FALSE)</f>
+      <c r="B15" s="11">
+        <f>VLOOKUP(B13,DrugParams!$A$2:$F$19,5,FALSE)</f>
         <v>3.7030000000000003E-5</v>
       </c>
-      <c r="C14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B15" s="2"/>
-      <c r="C15" s="3" t="s">
-        <v>25</v>
-      </c>
+      <c r="C15" s="9"/>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B16" s="2"/>
       <c r="C16" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="2"/>
+      <c r="C17" s="3" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="24.75" x14ac:dyDescent="0.25">
-      <c r="A17" s="5" t="s">
+    <row r="18" spans="1:3" ht="24.75" x14ac:dyDescent="0.25">
+      <c r="A18" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="10">
-        <f>IF(B15="",B13,B15)</f>
+      <c r="B18" s="10">
+        <f>IF(B16="",B14,B16)</f>
         <v>387.28</v>
       </c>
-      <c r="C17" s="3" t="s">
+      <c r="C18" s="3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="5" t="s">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A19" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="B18" s="11">
-        <f>IF(B16="",B14,B16)</f>
+      <c r="B19" s="11">
+        <f>IF(B17="",B15,B17)</f>
         <v>3.7030000000000003E-5</v>
       </c>
-      <c r="C18" s="9"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="24" t="s">
+      <c r="C19" s="9"/>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A21" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="23"/>
-      <c r="C20" s="23"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="5" t="s">
+      <c r="B21" s="24"/>
+      <c r="C21" s="24"/>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A22" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="6">
-        <f>SQRT((B17/1000000)/B18)</f>
+      <c r="B22" s="6">
+        <f>SQRT((B18/1000000)/B19)</f>
         <v>3.2339677060777139</v>
       </c>
-      <c r="C21" s="5"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="5" t="s">
+      <c r="C22" s="5"/>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A23" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="6">
-        <f>LN(2)/B18/3600</f>
+      <c r="B23" s="6">
+        <f>LN(2)/B19/3600</f>
         <v>5.19959177663715</v>
       </c>
-      <c r="C22" s="5"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="5" t="s">
+      <c r="C23" s="5"/>
+    </row>
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A24" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="B23" s="6">
-        <f>IF(B7="Slab",100/COSH(B10/B21),IF(B7="Cylinder",100/BESSELI(B10/B21,0),100*(B10/B21)/SINH(B10/B21)))</f>
+      <c r="B24" s="6">
+        <f>IF(B8="Slab",100/COSH(B11/B22),IF(B8="Cylinder",100/BESSELI(B11/B22,0),100*(B11/B22)/SINH(B11/B22)))</f>
         <v>8.9423360634446905E-2</v>
       </c>
-      <c r="C23" s="5"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="5" t="s">
+      <c r="C24" s="5"/>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A25" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="B24" s="12" t="str">
-        <f>IF(B23/100&gt;=B11,"Reachable","NR (Css&lt;M)")</f>
+      <c r="B25" s="12" t="str">
+        <f>IF(B24/100&gt;=B12,"Reachable","NR (Css&lt;M)")</f>
         <v>NR (Css&lt;M)</v>
       </c>
-      <c r="C24" s="13" t="s">
+      <c r="C25" s="13" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="5" t="s">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B25" s="6">
-        <f>B21*ACOSH(1/B11)</f>
+      <c r="B26" s="6">
+        <f>B22*ACOSH(1/B12)</f>
         <v>17.134506407742403</v>
       </c>
-      <c r="C25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="5" t="s">
+      <c r="C26" s="5"/>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A27" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B26" s="6">
-        <f>4*PI()/3*POWER(B25,3)/1000</f>
+      <c r="B27" s="6">
+        <f>4*PI()/3*POWER(B26,3)/1000</f>
         <v>21.071885806920271</v>
       </c>
-      <c r="C26" s="5"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="5" t="s">
+      <c r="C27" s="5"/>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A28" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B27" s="11">
-        <f>IF(B7&lt;&gt;"Slab","(slab only)",(B17/1000000)/POWER((B10/ACOSH(1/B11)),2))</f>
+      <c r="B28" s="11">
+        <f>IF(B8&lt;&gt;"Slab","(slab only)",(B18/1000000)/POWER((B11/ACOSH(1/B12)),2))</f>
         <v>1.7474861553269999E-5</v>
       </c>
-      <c r="C27" s="5"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="5" t="s">
+      <c r="C28" s="5"/>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A29" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B28" s="10">
-        <f>IF(B7&lt;&gt;"Slab","(slab only)",B18/B27)</f>
+      <c r="B29" s="10">
+        <f>IF(B8&lt;&gt;"Slab","(slab only)",B19/B28)</f>
         <v>2.1190439699403929</v>
       </c>
-      <c r="C28" s="5"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="5" t="s">
+      <c r="C29" s="5"/>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B29" s="8" t="str">
-        <f>IF(B7&lt;&gt;"Slab","Use steady-state % + d_crit for non-slab geometries",IF(B28&lt;=1,"Reachable at steady state","NR at steady state"))</f>
+      <c r="B30" s="8" t="str">
+        <f>IF(B8&lt;&gt;"Slab","Use steady-state % + d_crit for non-slab geometries",IF(B29&lt;=1,"Reachable at steady state","NR at steady state"))</f>
         <v>NR at steady state</v>
       </c>
-      <c r="C29" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="24" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
         <v>43</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="14" t="s">
+      <c r="B32" s="24"/>
+      <c r="C32" s="24"/>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A33" s="14" t="s">
         <v>44</v>
       </c>
-      <c r="B32" s="14" t="s">
+      <c r="B33" s="14" t="s">
         <v>45</v>
       </c>
-      <c r="C32" s="14" t="s">
+      <c r="C33" s="14" t="s">
         <v>46</v>
       </c>
-      <c r="D32" s="14" t="s">
+      <c r="D33" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="E32" s="14" t="s">
+      <c r="E33" s="14" t="s">
         <v>48</v>
       </c>
-      <c r="F32" s="14" t="s">
+      <c r="F33" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G33" s="14" t="s">
         <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="2">
-        <v>1</v>
-      </c>
-      <c r="B33" s="15">
-        <f>A33*5</f>
-        <v>5</v>
-      </c>
-      <c r="C33" s="15">
-        <f>IF(B7="Slab",100/COSH(B33/B21),IF(B7="Cylinder",100/BESSELI(B33/B21,0),100*(B33/B21)/SINH(B33/B21)))</f>
-        <v>40.765106568284821</v>
-      </c>
-      <c r="D33" s="16" t="str">
-        <f>IF(C33&gt;=1,"Reachable","NR")</f>
-        <v>Reachable</v>
-      </c>
-      <c r="E33" s="16" t="str">
-        <f>IF(C33&gt;=10,"Reachable","NR")</f>
-        <v>Reachable</v>
-      </c>
-      <c r="F33" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A33&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
-        <v>1.1729015531167679</v>
-      </c>
-      <c r="G33" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A33&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
-        <v>2.618081518508816</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A34" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B34" s="15">
         <f>A34*5</f>
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="C34" s="15">
-        <f>IF(B7="Slab",100/COSH(B34/B21),IF(B7="Cylinder",100/BESSELI(B34/B21,0),100*(B34/B21)/SINH(B34/B21)))</f>
-        <v>9.0619219005784775</v>
+        <f>IF(B8="Slab",100/COSH(B34/B22),IF(B8="Cylinder",100/BESSELI(B34/B22,0),100*(B34/B22)/SINH(B34/B22)))</f>
+        <v>40.765106568284821</v>
       </c>
       <c r="D34" s="16" t="str">
         <f>IF(C34&gt;=1,"Reachable","NR")</f>
@@ -1720,98 +1677,119 @@
       </c>
       <c r="E34" s="16" t="str">
         <f>IF(C34&gt;=10,"Reachable","NR")</f>
-        <v>NR</v>
+        <v>Reachable</v>
       </c>
       <c r="F34" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A34&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
-        <v>5.2257932015642901</v>
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A34&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
+        <v>1.1729015531167679</v>
       </c>
       <c r="G34" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A34&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
-        <v>0</v>
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A34&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
+        <v>2.618081518508816</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A35" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="B35" s="15">
         <f>A35*5</f>
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="C35" s="15">
-        <f>IF(B7="Slab",100/COSH(B35/B21),IF(B7="Cylinder",100/BESSELI(B35/B21,0),100*(B35/B21)/SINH(B35/B21)))</f>
-        <v>8.7849962264611794E-2</v>
+        <f>IF(B8="Slab",100/COSH(B35/B22),IF(B8="Cylinder",100/BESSELI(B35/B22,0),100*(B35/B22)/SINH(B35/B22)))</f>
+        <v>9.0619219005784775</v>
       </c>
       <c r="D35" s="16" t="str">
         <f>IF(C35&gt;=1,"Reachable","NR")</f>
-        <v>NR</v>
+        <v>Reachable</v>
       </c>
       <c r="E35" s="16" t="str">
         <f>IF(C35&gt;=10,"Reachable","NR")</f>
         <v>NR</v>
       </c>
       <c r="F35" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A35&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A35&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
+        <v>5.2257932015642901</v>
+      </c>
+      <c r="G35" s="15">
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A35&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
         <v>0</v>
       </c>
-      <c r="G35" s="15">
-        <f>IF(COUNTA($B$15:$B$16)&gt;0,"Use Python",VLOOKUP($B$12&amp;" | L="&amp;A35&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="2">
+        <v>5</v>
+      </c>
+      <c r="B36" s="15">
+        <f>A36*5</f>
+        <v>25</v>
+      </c>
+      <c r="C36" s="15">
+        <f>IF(B8="Slab",100/COSH(B36/B22),IF(B8="Cylinder",100/BESSELI(B36/B22,0),100*(B36/B22)/SINH(B36/B22)))</f>
+        <v>8.7849962264611794E-2</v>
+      </c>
+      <c r="D36" s="16" t="str">
+        <f>IF(C36&gt;=1,"Reachable","NR")</f>
+        <v>NR</v>
+      </c>
+      <c r="E36" s="16" t="str">
+        <f>IF(C36&gt;=10,"Reachable","NR")</f>
+        <v>NR</v>
+      </c>
+      <c r="F36" s="15">
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A36&amp;" cm",ClinicalLookup!$A$2:$J$55,8,FALSE))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="26" t="s">
+      <c r="G36" s="15">
+        <f>IF(COUNTA($B$16:$B$17)&gt;0,"Use Python",VLOOKUP($B$13&amp;" | L="&amp;A36&amp;" cm",ClinicalLookup!$A$2:$J$55,10,FALSE))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="23"/>
-      <c r="E37" s="23"/>
-      <c r="F37" s="23"/>
-      <c r="G37" s="23"/>
+      <c r="B38" s="24"/>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="A38:G38"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A3:G3"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
-  <conditionalFormatting sqref="B24">
-    <cfRule type="expression" dxfId="5" priority="1">
-      <formula>ISNUMBER(SEARCH("Reachable",B24))</formula>
+  <conditionalFormatting sqref="B25">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>ISNUMBER(SEARCH("Reachable",B25))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="2">
-      <formula>ISNUMBER(SEARCH("NR",B24))</formula>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>ISNUMBER(SEARCH("NR",B25))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D33:D35">
-    <cfRule type="expression" dxfId="3" priority="3">
-      <formula>ISNUMBER(SEARCH("Reachable",D33))</formula>
+  <conditionalFormatting sqref="D34:E36">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>ISNUMBER(SEARCH("Reachable",D34))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="4">
-      <formula>ISNUMBER(SEARCH("NR",D33))</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E33:E35">
-    <cfRule type="expression" dxfId="1" priority="5">
-      <formula>ISNUMBER(SEARCH("Reachable",E33))</formula>
-    </cfRule>
-    <cfRule type="expression" dxfId="0" priority="6">
-      <formula>ISNUMBER(SEARCH("NR",E33))</formula>
+    <cfRule type="expression" dxfId="0" priority="4">
+      <formula>ISNUMBER(SEARCH("NR",D34))</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" sqref="B5" xr:uid="{00000000-0002-0000-0000-000000000000}">
+    <dataValidation type="list" sqref="B6" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Edaravone,Fasudil,MgSO4,Uric Acid,NXY-059,Minocycline"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B6" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="B7" xr:uid="{00000000-0002-0000-0000-000001000000}">
       <formula1>"Mid-case,Conservative,Permissive"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="B7" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="B8" xr:uid="{00000000-0002-0000-0000-000002000000}">
       <formula1>"Slab,Cylinder,Sphere"</formula1>
     </dataValidation>
   </dataValidations>
@@ -3938,11 +3916,11 @@
         <v>3.3510321638291124E-2</v>
       </c>
       <c r="C4" s="19">
-        <f>100/COSH(A4/Calculator!$B$21)</f>
+        <f>100/COSH(A4/Calculator!$B$22)</f>
         <v>83.513982574682686</v>
       </c>
       <c r="D4" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E4" s="5" t="str">
@@ -3959,11 +3937,11 @@
         <v>0.26808257310632899</v>
       </c>
       <c r="C5" s="19">
-        <f>100/COSH(A5/Calculator!$B$21)</f>
+        <f>100/COSH(A5/Calculator!$B$22)</f>
         <v>53.545974837268616</v>
       </c>
       <c r="D5" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E5" s="5" t="str">
@@ -3980,11 +3958,11 @@
         <v>0.90477868423386032</v>
       </c>
       <c r="C6" s="19">
-        <f>100/COSH(A6/Calculator!$B$21)</f>
+        <f>100/COSH(A6/Calculator!$B$22)</f>
         <v>30.534071047451217</v>
       </c>
       <c r="D6" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E6" s="5" t="str">
@@ -4001,11 +3979,11 @@
         <v>2.1446605848506319</v>
       </c>
       <c r="C7" s="19">
-        <f>100/COSH(A7/Calculator!$B$21)</f>
+        <f>100/COSH(A7/Calculator!$B$22)</f>
         <v>16.73495656656192</v>
       </c>
       <c r="D7" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E7" s="5" t="str">
@@ -4022,11 +4000,11 @@
         <v>4.1887902047863905</v>
       </c>
       <c r="C8" s="19">
-        <f>100/COSH(A8/Calculator!$B$21)</f>
+        <f>100/COSH(A8/Calculator!$B$22)</f>
         <v>9.0619219005784775</v>
       </c>
       <c r="D8" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E8" s="5" t="str">
@@ -4043,11 +4021,11 @@
         <v>7.2382294738708826</v>
       </c>
       <c r="C9" s="19">
-        <f>100/COSH(A9/Calculator!$B$21)</f>
+        <f>100/COSH(A9/Calculator!$B$22)</f>
         <v>4.8895825762940293</v>
       </c>
       <c r="D9" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E9" s="5" t="str">
@@ -4064,11 +4042,11 @@
         <v>11.494040321933856</v>
       </c>
       <c r="C10" s="19">
-        <f>100/COSH(A10/Calculator!$B$21)</f>
+        <f>100/COSH(A10/Calculator!$B$22)</f>
         <v>2.6355611222306492</v>
       </c>
       <c r="D10" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E10" s="5" t="str">
@@ -4085,11 +4063,11 @@
         <v>17.157284678805055</v>
       </c>
       <c r="C11" s="19">
-        <f>100/COSH(A11/Calculator!$B$21)</f>
+        <f>100/COSH(A11/Calculator!$B$22)</f>
         <v>1.4201805575206534</v>
       </c>
       <c r="D11" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E11" s="5" t="str">
@@ -4106,11 +4084,11 @@
         <v>24.429024474314229</v>
       </c>
       <c r="C12" s="19">
-        <f>100/COSH(A12/Calculator!$B$21)</f>
+        <f>100/COSH(A12/Calculator!$B$22)</f>
         <v>0.76520189822935414</v>
       </c>
       <c r="D12" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E12" s="5" t="str">
@@ -4127,11 +4105,11 @@
         <v>33.510321638291124</v>
       </c>
       <c r="C13" s="19">
-        <f>100/COSH(A13/Calculator!$B$21)</f>
+        <f>100/COSH(A13/Calculator!$B$22)</f>
         <v>0.41228495228035567</v>
       </c>
       <c r="D13" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E13" s="5" t="str">
@@ -4148,11 +4126,11 @@
         <v>44.602238100565486</v>
       </c>
       <c r="C14" s="19">
-        <f>100/COSH(A14/Calculator!$B$21)</f>
+        <f>100/COSH(A14/Calculator!$B$22)</f>
         <v>0.22213435300575335</v>
       </c>
       <c r="D14" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E14" s="5" t="str">
@@ -4169,11 +4147,11 @@
         <v>57.90583579096706</v>
       </c>
       <c r="C15" s="19">
-        <f>100/COSH(A15/Calculator!$B$21)</f>
+        <f>100/COSH(A15/Calculator!$B$22)</f>
         <v>0.1196831582056507</v>
       </c>
       <c r="D15" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E15" s="5" t="str">
@@ -4190,11 +4168,11 @@
         <v>73.622176639325602</v>
       </c>
       <c r="C16" s="19">
-        <f>100/COSH(A16/Calculator!$B$21)</f>
+        <f>100/COSH(A16/Calculator!$B$22)</f>
         <v>6.4483720163424824E-2</v>
       </c>
       <c r="D16" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E16" s="5" t="str">
@@ -4211,11 +4189,11 @@
         <v>91.952322575470845</v>
       </c>
       <c r="C17" s="19">
-        <f>100/COSH(A17/Calculator!$B$21)</f>
+        <f>100/COSH(A17/Calculator!$B$22)</f>
         <v>3.4742978698476749E-2</v>
       </c>
       <c r="D17" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E17" s="5" t="str">
@@ -4232,11 +4210,11 @@
         <v>113.09733552923254</v>
       </c>
       <c r="C18" s="19">
-        <f>100/COSH(A18/Calculator!$B$21)</f>
+        <f>100/COSH(A18/Calculator!$B$22)</f>
         <v>1.8719058121663659E-2</v>
       </c>
       <c r="D18" s="19">
-        <f>Calculator!$B$11*100</f>
+        <f>Calculator!$B$12*100</f>
         <v>1</v>
       </c>
       <c r="E18" s="5" t="str">
